--- a/code-device-research-sources/device_evidence.xlsx
+++ b/code-device-research-sources/device_evidence.xlsx
@@ -7,14 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clinical trials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trial passages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI verification" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanism passages" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanism sources" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Passages'!$A$1:$X$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$P$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Codebook'!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Passages'!$A$1:$X$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sources'!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Codebook'!$A$1:$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -72,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -82,6 +87,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -160,7 +168,78 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PassagesTable" displayName="PassagesTable" ref="A1:X23" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ClinicaltrialsTable" displayName="ClinicaltrialsTable" ref="A1:W8" headerRowCount="1">
+  <autoFilter ref="A1:W8"/>
+  <tableColumns count="23">
+    <tableColumn id="1" name="study_id"/>
+    <tableColumn id="2" name="study"/>
+    <tableColumn id="3" name="device"/>
+    <tableColumn id="4" name="doi"/>
+    <tableColumn id="5" name="registry_id"/>
+    <tableColumn id="6" name="first_publication_date"/>
+    <tableColumn id="7" name="design"/>
+    <tableColumn id="8" name="publication_cohort"/>
+    <tableColumn id="9" name="follow_up"/>
+    <tableColumn id="10" name="primary_endpoint"/>
+    <tableColumn id="11" name="principal_result"/>
+    <tableColumn id="12" name="lead_sponsor"/>
+    <tableColumn id="13" name="funding"/>
+    <tableColumn id="14" name="oversight_or_analysis"/>
+    <tableColumn id="15" name="independence_class"/>
+    <tableColumn id="16" name="ai_effect_isolated"/>
+    <tableColumn id="17" name="applicability"/>
+    <tableColumn id="18" name="limitations"/>
+    <tableColumn id="19" name="access_level"/>
+    <tableColumn id="20" name="source_url"/>
+    <tableColumn id="21" name="registry_url"/>
+    <tableColumn id="22" name="abstract_record"/>
+    <tableColumn id="23" name="accessed_date"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TrialpassagesTable" displayName="TrialpassagesTable" ref="A1:L19" headerRowCount="1">
+  <autoFilter ref="A1:L19"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="passage_id"/>
+    <tableColumn id="2" name="study_id"/>
+    <tableColumn id="3" name="study"/>
+    <tableColumn id="4" name="quote"/>
+    <tableColumn id="5" name="locator"/>
+    <tableColumn id="6" name="code"/>
+    <tableColumn id="7" name="interpretation"/>
+    <tableColumn id="8" name="source_url"/>
+    <tableColumn id="9" name="doi"/>
+    <tableColumn id="10" name="publication_date"/>
+    <tableColumn id="11" name="accessed_date"/>
+    <tableColumn id="12" name="verification"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AIverificationTable" displayName="AIverificationTable" ref="A1:I7" headerRowCount="1">
+  <autoFilter ref="A1:I7"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="device"/>
+    <tableColumn id="2" name="verification_verdict"/>
+    <tableColumn id="3" name="mechanism"/>
+    <tableColumn id="4" name="processing_location"/>
+    <tableColumn id="5" name="training_or_model_evidence"/>
+    <tableColumn id="6" name="validation_scope"/>
+    <tableColumn id="7" name="evidence_ids"/>
+    <tableColumn id="8" name="confidence_and_limits"/>
+    <tableColumn id="9" name="safe_description"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PassagesTable" displayName="PassagesTable" ref="A1:X23" headerRowCount="1">
   <autoFilter ref="A1:X23"/>
   <tableColumns count="24">
     <tableColumn id="1" name="passage_id"/>
@@ -192,8 +271,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourcesTable" displayName="SourcesTable" ref="A1:P7" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SourcesTable" displayName="SourcesTable" ref="A1:P7" headerRowCount="1">
   <autoFilter ref="A1:P7"/>
   <tableColumns count="16">
     <tableColumn id="1" name="source_id"/>
@@ -217,13 +296,54 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CodebookTable" displayName="CodebookTable" ref="A1:C17" headerRowCount="1">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CodebookTable" displayName="CodebookTable" ref="A1:C17" headerRowCount="1">
   <autoFilter ref="A1:C17"/>
   <tableColumns count="3">
     <tableColumn id="1" name="code"/>
     <tableColumn id="2" name="definition"/>
     <tableColumn id="3" name="paper_derivation"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="MechanismpassagesTable" displayName="MechanismpassagesTable" ref="A1:N14" headerRowCount="1">
+  <autoFilter ref="A1:N14"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="passage_id"/>
+    <tableColumn id="2" name="source_id"/>
+    <tableColumn id="3" name="device"/>
+    <tableColumn id="4" name="locator"/>
+    <tableColumn id="5" name="quote"/>
+    <tableColumn id="6" name="code"/>
+    <tableColumn id="7" name="interpretation"/>
+    <tableColumn id="8" name="creator"/>
+    <tableColumn id="9" name="source_date"/>
+    <tableColumn id="10" name="source_title"/>
+    <tableColumn id="11" name="url"/>
+    <tableColumn id="12" name="accessed_date"/>
+    <tableColumn id="13" name="verification"/>
+    <tableColumn id="14" name="rights"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="MechanismsourcesTable" displayName="MechanismsourcesTable" ref="A1:I6" headerRowCount="1">
+  <autoFilter ref="A1:I6"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="source_id"/>
+    <tableColumn id="2" name="creator"/>
+    <tableColumn id="3" name="source_date"/>
+    <tableColumn id="4" name="title"/>
+    <tableColumn id="5" name="url"/>
+    <tableColumn id="6" name="source_type"/>
+    <tableColumn id="7" name="rights"/>
+    <tableColumn id="8" name="historical_relevance"/>
+    <tableColumn id="9" name="limitations"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -518,6 +638,2584 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:W8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
+    <col width="56" customWidth="1" min="13" max="13"/>
+    <col width="56" customWidth="1" min="14" max="14"/>
+    <col width="56" customWidth="1" min="15" max="15"/>
+    <col width="56" customWidth="1" min="16" max="16"/>
+    <col width="56" customWidth="1" min="17" max="17"/>
+    <col width="56" customWidth="1" min="18" max="18"/>
+    <col width="56" customWidth="1" min="19" max="19"/>
+    <col width="56" customWidth="1" min="20" max="20"/>
+    <col width="56" customWidth="1" min="21" max="21"/>
+    <col width="56" customWidth="1" min="22" max="22"/>
+    <col width="56" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>registry_id</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>first_publication_date</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>publication_cohort</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>primary_endpoint</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>principal_result</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>lead_sponsor</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>funding</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>oversight_or_analysis</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>independence_class</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>ai_effect_isolated</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>applicability</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>limitations</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>access_level</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>registry_url</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>abstract_record</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>accessed_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PRAETORIAN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Subcutaneous ICD vs transvenous ICD</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa1915932</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NCT01296022</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2020-08-06</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Investigator-initiated randomized noninferiority; modified intention-to-treat</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>876 randomized; 849 analyzed (426 S-ICD / 423 TV-ICD)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Median 49.1 months</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Device-related complications or inappropriate shocks</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>48-month cumulative incidence 15.1% vs 15.7%; HR 0.99 (95% CI 0.71–1.39); noninferiority P=0.01; superiority P=0.95</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Academic Medical Center Amsterdam</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Investigators designed and analyzed; company reported no role in design/analysis/manuscript; independent DSMB and clinical-events committee</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Academic-led / industry-funded</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Supports S-ICD component and lead-avoidance rationale, not combined EMPOWER system or AI</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Excludes pacing indication; not an EMPOWER trial; 27 post-randomization exclusions; no established superiority for primary composite</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Full primary article read from public hospital-hosted PDF; copyrighted, not verified open-licensed</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.valleyhealth.com/sites/default/files/2020-09/PRAETORIAN%20NEJM%202020.pdf</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT01296022</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/article/MED/32757521</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ATLAS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EMBLEM S-ICD vs transvenous ICD</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>10.7326/M22-1566</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>NCT02881255</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Investigator-sponsored randomized multicenter open-label parallel group</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>544 eligible screened; 503 randomized (251 / 252)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Primary endpoint six months; mean follow-up 2.5 years</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Major perioperative lead-related complications</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1/251 (0.4%) vs 12/252 (4.8%); risk difference −4.4 percentage points (95% CI −6.9 to −1.9); journal P=0.001</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Population Health Research Institute</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>PHRI trial; expert committee central adjudication and DSMB described in investigator slides; manufacturer role in all analyses not established from abstract/slides</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Academic-led / industry-funded</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Directly supports component-level lead complication claims, not AI or combined EMPOWER therapy</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Underpowered for shock outcomes; early pain greater with S-ICD; inappropriate-shock HR 2.37 (95% CI 0.98–5.77); cohort selected for age/risk</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Primary journal abstract via Europe PMC; primary investigator slides and PHRI site read; journal full text HTTP 403</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7326/M22-1566</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT02881255</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/article/MED/36343346</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Qinming8631 DR noninferiority trial</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Qinming8631 DR vs Talos DR</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10.4103/0366-6999.193443</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2016-11-20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Prospective randomized multicenter single-blind noninferiority</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>225 randomized (113 / 112)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Six months</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Effective pacing rate</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>FAS: 81.4% vs 79.5%; PPS: 95.4% vs 89.5%; authors report noninferiority with predefined −9.5% limit</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Institutional clinical investigators; formal registry sponsor not verified</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Article reports financial support and sponsorship: Nil</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Article describes third-party data processing/statistical analyst; no conflicts declared; external sponsor-control audit unavailable</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>No sponsorship reported / independence not fully verified</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Direct Qinming pacing comparison; AI integration not established; QM7211 is a ventricular lead</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>87/113 and 86/112 in per-protocol completion set; six-month duration; do not treat noninferiority as superiority</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Original full article read in existing corpus and verified abstract; publisher marks Open, precise licence unresolved</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>https://journals.lww.com/cmj/fulltext/2016/11200/evaluation_of_safety_and_efficacy_of_qinming8631.3.aspx</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/article/MED/27823996</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MARVEL 2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Micra accelerometer-based AV algorithm; predecessor evidence</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.jacep.2019.10.017</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>NCT03752151</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2019-11-11</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Prospective acute within-patient VDD vs VVI-50 comparison; not randomized parallel group</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75 with algorithm download; efficacy subset 40; current registry enrollment 77</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Up to five hours</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Proportion with ≥70% AV synchrony at rest</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>95% with VDD vs 0% with VVI (P&lt;0.001); mean AV synchrony 89.2% vs 26.8%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Medtronic Cardiac Rhythm and Heart Failure</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Industry-sponsored; exact funding language in full article not separately audited</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Registry notes masked echo core lab; sponsor is Medtronic</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer-sponsored comparator evidence</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Tests sensor-driven algorithm performance; not ML validation; not a direct Micra AV2/VR2 trial</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Acute surrogate endpoint; predecessor device/software; no long-term outcome comparison</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Primary article abstract via Europe PMC plus registry; full article not reviewed</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jacep.2019.10.017</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT03752151</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/article/MED/31709982</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AccelAV</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Micra AV, not Micra AV2/VR2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.hrthm.2022.08.033</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>NCT04245345</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Prospective multicenter single-arm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>152 enrolled and implanted; primary subset 54; optimization subset 20; current registry enrollment 157</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Primary endpoint one month; follow-up through three months</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Resting AV synchrony in complete AV block and normal sinus function</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Primary subset mean resting AV synchrony 85.4%; ambulatory 74.8%; optimization subset ambulatory 82.6%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Medtronic Cardiac Rhythm and Heart Failure</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Medtronic (registry sponsor and indexed grant information)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Independent sponsor control of analysis not established from abstract</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer-sponsored comparator evidence</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Clinical follow-up of mechanical atrial sensing; no AI-specific contrast; generation mismatch to AV2/VR2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Single arm; selected subsets; optimization percentage not whole-cohort result; quality-of-life change not causal comparative effect</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract plus registry; publisher full text HTTP 403</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.hrthm.2022.08.033</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT04245345</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/article/MED/36075532</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR i2i pivotal trial</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR dual-chamber leadless pacing</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>NCT05252702</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Prospective multicenter single-group against performance goals</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>300 in 2023 paper; current registry enrollment 464</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90 days / three months</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Freedom from serious device/procedure complications; electrical performance; ≥70% AV synchrony</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Implant success 295/300 (98.3%); safety 271/300 (90.3%, 95% CI 87.0–93.7); 29 patients had 35 serious events; AV synchrony criterion met by 97.3%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Abbott Medical Devices</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Abbott Medical</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Separate independent adjudication/analysis not verified from abstract; industry sponsor established</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer-sponsored comparator evidence</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Direct AVEIR DR evidence; communication/pacing performance, not AI benefit</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Single group; 97.3% is patients achieving ≥70% synchrony, not average synchrony; 98.3% implant success is not 90-day safety</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract via Europe PMC plus registry; journal full text not reviewed</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT05252702</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/article/MED/37212442</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MODULAR ATP</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EMBLEM S-ICD + EMPOWER</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2401807</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NCT04798768</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Prospective multinational single-group against performance goals</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>293 enrolled; six-month endpoint cohort 162; 151 completed six-month visit; current registry 297</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Six-month primary endpoints</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Freedom from major leadless-pacemaker complications; communication success; pacing threshold</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>97.5% free from major pacemaker complications; 98.8% of communication tests successful; 147/151 (97.4%) acceptable pacing threshold</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Boston Scientific Corporation</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Independent monitoring and clinical-events committees; sponsor collected/monitored data and performed outcome analyses</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer-sponsored / independent adjudication</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Direct combined-system clinical evidence; no AI-specific contrast; later update only</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Published after February 2024 paper; performance goals not concurrent controls; endpoint cohort smaller than enrollment</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Full primary article publicly reachable via clinical mirror; copyrighted, no open reuse licence verified</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cardioaragon.com/wp-content/uploads/A-Modular-Communicative-Leadless.NEJMed.2024.pdf</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/study/NCT04798768</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/article/MED/38767244</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T8" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId20"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>passage_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>interpretation</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>publication_date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>accessed_date</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>PRAETORIAN</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>We conducted this investigator-initiated, international, randomized, noninferiority trial in the United States and Europe.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Article p.527, Trial Design and Oversight</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>GOVERNANCE</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Academic initiation, not industry-free funding.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.valleyhealth.com/sites/default/files/2020-09/PRAETORIAN%20NEJM%202020.pdf</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa1915932</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2020-08-06</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PRAETORIAN</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>This trial was funded by Boston Scientific, which had no role in the design of the trial, analysis of the data, or the drafting and submission of the manuscript.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Article p.527, Trial Design and Oversight</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FUNDING_ROLE</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Industry funding with reported investigator control.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.valleyhealth.com/sites/default/files/2020-09/PRAETORIAN%20NEJM%202020.pdf</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa1915932</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2020-08-06</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PRAETORIAN</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A clinical-events committee consisting of three electrophysiologists who were not otherwise involved in the trial adjudicated all clinical and arrhythmic events.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Article p.528, End Points</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Independent event review is a separate dimension from funding.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.valleyhealth.com/sites/default/files/2020-09/PRAETORIAN%20NEJM%202020.pdf</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa1915932</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2020-08-06</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ATLAS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Investigator Sponsored Trial with funding from Boston Scientific</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>HRS 2022 investigator presentation, slide 5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FUNDING_ROLE</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Academic sponsorship does not mean no manufacturer funding.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phri.ca/wp-content/uploads/2022/04/ATLAS-S-ICD_HRS2022-1.pdf</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10.7326/M22-1566</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ATLAS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>which occurred in 1 patient (0.4%) with an S-ICD and in 12 patients (4.8%) with TV-ICD</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Primary journal abstract &gt; Results</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>CLINICAL_OUTCOME</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Lead-related complications; not an AI effect.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7326/M22-1566</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10.7326/M22-1566</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ATLAS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>At present, the ATLAS trial is underpowered to detect differences in clinical shock outcomes; however, extended follow-up is ongoing.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Primary journal abstract &gt; Limitation</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>INFERENCE_LIMIT</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Nonsignificant shock differences do not establish equivalent shock outcomes.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7326/M22-1566</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10.7326/M22-1566</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Qinming8631 DR noninferiority trial</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nil.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Original article &gt; Financial support and sponsorship</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>FUNDING_ROLE</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Self-reported absence of sponsorship, not external verification of independence.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://journals.lww.com/cmj/fulltext/2016/11200/evaluation_of_safety_and_efficacy_of_qinming8631.3.aspx</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10.4103/0366-6999.193443</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2016-11-20</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Qinming8631 DR noninferiority trial</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Data were collected at each clinical site by a third-party analyzer who was responsible for data processing and statistical analysis.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Original article &gt; Methods &gt; Study design</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ANALYSIS_ROLE</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Reported third-party processing; identity and contract independence not established.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>https://journals.lww.com/cmj/fulltext/2016/11200/evaluation_of_safety_and_efficacy_of_qinming8631.3.aspx</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10.4103/0366-6999.193443</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2016-11-20</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>MARVEL 2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>downloaded to the Micra leadless pacemaker for up to 5 h in patients with AV block.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract &gt; Methods</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>FOLLOWUP_LIMIT</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Acute algorithm assessment, not a chronic AI clinical trial.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jacep.2019.10.017</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.jacep.2019.10.017</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2019-11-11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MARVEL 2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Among the 40 patients with sinus rhythm and complete AV block included in the primary efficacy objective analysis</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract &gt; Results</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>DENOMINATOR</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Efficacy subset is not all 75 participants.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jacep.2019.10.017</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.jacep.2019.10.017</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2019-11-11</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AccelAV</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>AccelAV was a prospective, single-arm study to characterize AVS in patients implanted with a Micra AV</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract &gt; Methods</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>TRIAL_DESIGN</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No randomized concurrent control; Micra AV is a predecessor generation.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.hrthm.2022.08.033</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.hrthm.2022.08.033</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>AccelAV</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Among patients with normal sinus function and complete AVB (n = 54), mean resting AVS was 85.4% at 1 month, and ambulatory AVS was 74.8%.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract &gt; Results</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>DENOMINATOR</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Report resting and ambulatory values separately; subset n=54.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.hrthm.2022.08.033</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.hrthm.2022.08.033</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR i2i pivotal trial</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>We conducted a prospective, multicenter, single-group study to evaluate the safety and performance of a dual-chamber leadless pacemaker system.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract &gt; Methods</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>TRIAL_DESIGN</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Performance-goal comparison, not randomized superiority.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR i2i pivotal trial</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>A total of 35 device- or procedure-related serious adverse events occurred in 29 patients.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract &gt; Results</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SAFETY</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Adds harms omitted from simplified implant-success reporting.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="150" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR i2i pivotal trial</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>At least 70% atrioventricular synchrony was achieved in 97.3% of the patients</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Primary abstract &gt; Results</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>DENOMINATOR</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>97.3% is proportion meeting a threshold, not a mean synchrony measure.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2300080</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>PASS: exact primary-abstract substring after whitespace normalization; retrieved via Europe PMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="150" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>MODULAR ATP</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>An independent clinical events committee reviewed adverse events and episodes of arrhythmia that were treated.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Article p.1403, Study Design and Oversight</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ADJUDICATION</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Independent adjudication present despite manufacturer sponsorship.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cardioaragon.com/wp-content/uploads/A-Modular-Communicative-Leadless.NEJMed.2024.pdf</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2401807</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>MODULAR ATP</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>The sponsor collected and monitored study data and performed outcome analyses according to the statistical analysis plan and the protocol</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Article p.1403, Study Design and Oversight</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ANALYSIS_ROLE</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Independent review does not mean sponsor-independent analysis.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cardioaragon.com/wp-content/uploads/A-Modular-Communicative-Leadless.NEJMed.2024.pdf</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2401807</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>MODULAR ATP</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>We enrolled 293 patients, 162 of whom were in the 6-month end-point cohort and 151 of whom completed the 6-month follow-up period.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Article p.1402, Abstract &gt; Results</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>DENOMINATOR</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Avoid attributing six-month endpoint denominators to all enrolled patients.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cardioaragon.com/wp-content/uploads/A-Modular-Communicative-Leadless.NEJMed.2024.pdf</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2401807</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Read primary full text/slide or primary abstract; PDF line-wrap hyphenation and whitespace normalized only</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>verification_verdict</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>processing_location</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>training_or_model_evidence</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>validation_scope</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>evidence_ids</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>confidence_and_limits</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>safe_description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="140" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BIOMONITOR IV / SmartECG</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AI-assisted AF classification verified; architecture unresolved</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Uploaded subcutaneous ECG → QRS/signal processing and AF AI classification → true/false episode label → clinician review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Home Monitoring Service Center, not implant or programmer</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Patient ECG training explicitly reported; evaluation excludes training contributors; model architecture, weights and complete training data not disclosed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>368 patients; 61,517 sECGs; balanced setting; observational/replayed workflow with IIIm recordings approximating IV</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>V01; M01–M05</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High for location and AF scope; insufficient for architecture or causal clinical benefit</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>AI-assisted remote ECG review associated with an implanted monitor; not implant-resident adaptive therapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="140" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Micra AV2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Automatic sensor-driven control verified; AI/ML not established</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical atrial activity sensed by accelerometer; A3/A4 threshold setup; Auto+ adjusts A3 threshold; Auto PVAB adjusts blanking by ventricular rate</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Implanted ventricular pacemaker</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>No trained statistical model or learning architecture identified in brochure</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer algorithm description; not a comparative AI trial</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>V02; M06–M08</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High for described mechanism; absence of ML documentation is not proof of no AI</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Leadless pacing with automatic mechanical atrial sensing and AV-synchrony optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="140" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Micra VR2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Rate-response capability verified; AV2 AI label unsupported</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Accelerometer-based rate response; mechanical atrial sensing listed N/A in p.4 specification table</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Implanted ventricular pacemaker</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>No learned model identified; AV2 atrial-sensing algorithms should not be assigned to VR2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>p.4 table checked as page image; not a patient-outcome evaluation</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>V02, p.4 (visual check)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High for feature distinction; limited for proprietary implementation</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Rate-responsive leadless ventricular pacemaker; distinguish from AV2 AV-synchronous sensing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="140" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR i2i</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Bidirectional electrical communication verified; AI/ML not established</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>RA and RV implants exchange conducted electrical signals beat-to-beat; programmable signal strength; wake-up and digital message protocol</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Two implanted pacemakers; programming sessions customize communication</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>No training process or learned predictor disclosed in engineering explanation</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer chief-engineer interview, 14 December 2023</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>V03; M09–M10</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High for vendor-described communication; not independent verification of all firmware</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Dual-chamber leadless pacing coordinated through implant-to-implant electrical communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="140" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EMBLEM S-ICD + EMPOWER</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Commanded ATP and programmed sensing verified; AI/ML not established</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>S-ICD sends request; EMPOWER receives command and paces; EMPOWER has programmable fixed-threshold sensing and accelerometer rate response</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Separate S-ICD and intracardiac EMPOWER</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>No learned model documented in examined protocol device/test sections; complete firmware not inspected</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Sponsor protocol Version I, 29 April 2022; communication test is not efficacy result</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>V04; M11–M12; pp.23,124–125,130</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High for specified command path; incomplete for every detection algorithm</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated modular defibrillation and pacing system; AI contribution remains unverified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="140" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Qinming8631 DR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Rate-responsive pacing documented; detailed mechanism unresolved</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Dual-chamber rate-responsive pacing tested; exact sensor and controller design not established by this trial</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Implanted pacemaker; detailed algorithm unavailable</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>No trained-model architecture or training protocol in trial report</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>225 randomized; six-month pacing noninferiority trial, not AI validation</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>V05 (= original S03); M13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High for trial scope; low for internal controller classification</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Dual-chamber rate-responsive pacemaker evaluated in a randomized noninferiority trial</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3194,7 +5892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3813,7 +6511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4123,4 +6821,1377 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="12" max="12"/>
+    <col width="58" customWidth="1" min="13" max="13"/>
+    <col width="58" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>passage_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>interpretation</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>creator</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>source_date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>source_title</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>accessed_date</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="140" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BIOMONITOR IV</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Methods &gt; SmartECG algorithm</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>SmartECG is a software package implemented in the HMSC for the BioMonitor IV ICM.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>LOCUS_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Confirms service-center computation, not implanted AI.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Bisignani et al.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Implantable cardiac monitors: artificial intelligence and signal processing reduce remote ECG review workload and preserve arrhythmia detection sensitivity</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/cardiovascular-medicine/articles/10.3389/fcvm.2024.1343424/full</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>CC BY; publicly readable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="140" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BIOMONITOR IV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Methods &gt; SmartECG algorithm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>For the analysis of AF events only, it further uses artificial intelligence, which can be set to different levels of strictness, from very sensitive to very specific.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>AI_EXPLICIT</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>AI limited to AF; remaining filtering includes signal processing.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Bisignani et al.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Implantable cardiac monitors: artificial intelligence and signal processing reduce remote ECG review workload and preserve arrhythmia detection sensitivity</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/cardiovascular-medicine/articles/10.3389/fcvm.2024.1343424/full</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>CC BY; publicly readable</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="140" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>BIOMONITOR IV</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Discussion &gt; Remote vs. in-office follow-up</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The SmartECG algorithm is implemented in the remote monitoring platform because it cannot be implemented in the ICM or in the programming device used to interrogate the ICM during a follow-up visit.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>LOCUS_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Directly rules out implant/programmer execution for this described SmartECG implementation.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Bisignani et al.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Implantable cardiac monitors: artificial intelligence and signal processing reduce remote ECG review workload and preserve arrhythmia detection sensitivity</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/cardiovascular-medicine/articles/10.3389/fcvm.2024.1343424/full</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>CC BY; publicly readable</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="140" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>BIOMONITOR IV</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Methods &gt; Data sources and patient populations</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>patients who had contributed sECGs to the training of SmartECG artificial intelligence algorithm for atrial fibrillation (AF) recognition.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>TRAINING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Excerpt from exclusion criterion: patient ECGs were used for training; excluded from evaluation. Architecture and complete training-set composition not disclosed.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Bisignani et al.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Implantable cardiac monitors: artificial intelligence and signal processing reduce remote ECG review workload and preserve arrhythmia detection sensitivity</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/cardiovascular-medicine/articles/10.3389/fcvm.2024.1343424/full</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>CC BY; publicly readable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="140" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>M05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>BIOMONITOR IV</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Methods &gt; SmartECG algorithm</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Our analysis uses the nominal “balanced” setting.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>VALIDATION_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Not the Very Specific setting behind the 2023 marketing claim.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Bisignani et al.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Implantable cardiac monitors: artificial intelligence and signal processing reduce remote ECG review workload and preserve arrhythmia detection sensitivity</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/cardiovascular-medicine/articles/10.3389/fcvm.2024.1343424/full</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>CC BY; publicly readable</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="140" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>M06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Micra AV2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>p. 12, Auto+ A3 Threshold</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Auto+ uses filtered, true A3 signal amplitudes to automatically set the A3 Threshold above the A3 signal, but below the A7 signal (summated A3 + A4 signal)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL_RULE</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Describes an adaptive threshold rule; no learned model specified.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Medtronic</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Micra leadless pacemakers; UC202002938e EN 05/2023</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://pdfs.semanticscholar.org/57d9/24ea3b36b976d9deeb0442f3d027ac70fc8d.pdf</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Medtronic; short attributed excerpts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="140" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>M07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Micra AV2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>p. 13, Auto PVAB and Upper Tracking Rate</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Micra AV2 offers an Auto PVAB algorithm which adjusts PVAB based on ventricular rate.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL_RULE</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Rate-dependent blanking control, not evidence of ML.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Medtronic</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Micra leadless pacemakers; UC202002938e EN 05/2023</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://pdfs.semanticscholar.org/57d9/24ea3b36b976d9deeb0442f3d027ac70fc8d.pdf</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Medtronic; short attributed excerpts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="140" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Micra AV2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>p. 11, Atrial Sensing Setup</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Micra AV2 will automatically set up AV synchrony parameters Atrial Sensing Vector, A3 and A4 Threshold, and A3 Window End related parameters after implant.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>AUTOMATION</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Device-local parameter setup; automatic does not establish ML.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Medtronic</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Micra leadless pacemakers; UC202002938e EN 05/2023</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://pdfs.semanticscholar.org/57d9/24ea3b36b976d9deeb0442f3d027ac70fc8d.pdf</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Medtronic; short attributed excerpts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR i2i</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Q: How do the leadless devices communicate?</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Unlike traditional wireless methods, i2i utilizes conducted electrical signaling akin to electrical Morse code.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>COMMUNICATION</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Electrical communication mechanism, not a learning algorithm.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Abbott Cardiac Rhythm Management</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-14</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Unveiling the i2i Communication Technology in the AVEIR DR Leadless Pacemaker (LP) System</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cardiovascular.abbott/us/en/hcp/products/cardiac-rhythm-management/blog/unveiling-the-i2i-communication-technology-in-aveir-dr.html</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Abbott; short attributed excerpts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="140" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>AVEIR DR i2i</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Q: What factors could impact i2i communication?</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The strength of i2i signals can be adjusted based on measurements of i2i functionality and additional diagnostics obtained during programming sessions, providing customization for each patient.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Clinical customization is documented; autonomous model training is not.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Abbott Cardiac Rhythm Management</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-14</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Unveiling the i2i Communication Technology in the AVEIR DR Leadless Pacemaker (LP) System</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cardiovascular.abbott/us/en/hcp/products/cardiac-rhythm-management/blog/unveiling-the-i2i-communication-technology-in-aveir-dr.html</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Abbott; short attributed excerpts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="140" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EMBLEM + EMPOWER</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Appendix A §26.1.1, p. 124</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Fixed threshold sensing with programmable sense threshold</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL_RULE</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly describes fixed/programmed sensing for EMPOWER; do not extrapolate to every S-ICD detection algorithm.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>MODULAR ATP Clinical Investigation Plan, 92272548, Version I; NCT04798768</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://cdn.clinicaltrials.gov/large-docs/68/NCT04798768/Prot_000.pdf</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Public registry download; copyrighted; marked Confidential / do not copy or distribute; only short attributed excerpts retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EMBLEM + EMPOWER</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Appendix C §26.3, p. 130</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Communication is tested by commanding a communication signal from the S-ICD System that, when successfully received by the EMPOWER PG, results in the EMPOWER PG delivering ATP therapy for up to 10 beats slightly faster than the subject’s intrinsic rate.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>COMMUNICATION</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Command-to-therapy relationship documented in protocol test; no ML described.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>MODULAR ATP Clinical Investigation Plan, 92272548, Version I; NCT04798768</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://cdn.clinicaltrials.gov/large-docs/68/NCT04798768/Prot_000.pdf</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Public registry download; copyrighted; marked Confidential / do not copy or distribute; only short attributed excerpts retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="140" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Qinming8631 DR</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Abstract &gt; Methods</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Electrical properties, magnet response, single- and double-pole polarity conversion, rate response function, and adverse events of the pacing system were analyzed.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMIT</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Trial assesses pacing functions but does not disclose a trained model or establish AI integration.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Xiang et al.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2016-11-20</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation of Safety and Efficacy of Qinming8631 DR Implantable Cardiac Pacemaker in Chinese Patients</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://journals.lww.com/cmj/fulltext/2016/11200/evaluation_of_safety_and_efficacy_of_qinming8631.3.aspx</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Full source read; HTML entities decoded / whitespace normalized; PDF line breaks joined</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Publisher marked Open; exact reuse licence not verified</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>creator</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>source_date</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>rights</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>historical_relevance</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>limitations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="140" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Bisignani et al.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Implantable cardiac monitors: artificial intelligence and signal processing reduce remote ECG review workload and preserve arrhythmia detection sensitivity</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.frontiersin.org/journals/cardiovascular-medicine/articles/10.3389/fcvm.2024.1343424/full</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Original pooled observational analysis</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>CC BY; publicly readable</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Before nominal February 2024 publication, after manuscript’s cited 16 January retrieval dates</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer-funded; Biotronik employee coauthor; BioMonitor IIIm recordings used to evaluate IV software workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="140" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Medtronic</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Micra leadless pacemakers; UC202002938e EN 05/2023</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://pdfs.semanticscholar.org/57d9/24ea3b36b976d9deeb0442f3d027ac70fc8d.pdf</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer technical brochure, 20 pages</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Medtronic; short attributed excerpts</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Contemporaneous; dated May 2023 in footer</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer PDF read from Semantic Scholar mirror; official download returned HTTP 403; p.4 visually checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="140" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Abbott Cardiac Rhythm Management</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Unveiling the i2i Communication Technology in the AVEIR DR Leadless Pacemaker (LP) System</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cardiovascular.abbott/us/en/hcp/products/cardiac-rhythm-management/blog/unveiling-the-i2i-communication-technology-in-aveir-dr.html</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer interview with chief engineer</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Copyright Abbott; short attributed excerpts</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Contemporaneous</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Engineering explanation, not an independent efficacy study</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="140" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>MODULAR ATP Clinical Investigation Plan, 92272548, Version I; NCT04798768</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://cdn.clinicaltrials.gov/large-docs/68/NCT04798768/Prot_000.pdf</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Publicly posted sponsor trial protocol, 148 pages</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Public registry download; copyrighted; marked Confidential / do not copy or distribute; only short attributed excerpts retained</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Document dated before paper; first public posting date not verified</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Read device and communication sections, not every protocol page; not a source-code audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="140" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Xiang et al.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2016-11-20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Evaluation of Safety and Efficacy of Qinming8631 DR Implantable Cardiac Pacemaker in Chinese Patients</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://journals.lww.com/cmj/fulltext/2016/11200/evaluation_of_safety_and_efficacy_of_qinming8631.3.aspx</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Original randomized trial; same document as S03</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Publisher marked Open; exact reuse licence not verified</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Contemporaneous</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Rate response assessed; detailed sensor/controller design not specified; no AI attribution established</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  </tableParts>
+</worksheet>
 </file>